--- a/notebooks/SHEM/tuning/DO_model_whole.xlsx
+++ b/notebooks/SHEM/tuning/DO_model_whole.xlsx
@@ -2663,43 +2663,43 @@
         <v>199.4013366699219</v>
       </c>
       <c r="AA19">
-        <v>73.94960021972656</v>
+        <v>111.7099227905273</v>
       </c>
       <c r="AB19">
-        <v>73.42434692382812</v>
+        <v>110.9164733886719</v>
       </c>
       <c r="AC19">
-        <v>73.30171966552734</v>
+        <v>110.7312240600586</v>
       </c>
       <c r="AD19">
-        <v>73.32028198242188</v>
+        <v>110.7592620849609</v>
       </c>
       <c r="AE19">
-        <v>73.31986999511719</v>
+        <v>110.7586364746094</v>
       </c>
       <c r="AF19">
-        <v>73.4012451171875</v>
+        <v>110.8815765380859</v>
       </c>
       <c r="AG19">
-        <v>73.28656005859375</v>
+        <v>110.7083282470703</v>
       </c>
       <c r="AH19">
-        <v>73.54226684570312</v>
+        <v>111.094596862793</v>
       </c>
       <c r="AI19">
-        <v>73.47636413574219</v>
+        <v>110.9950408935547</v>
       </c>
       <c r="AJ19">
-        <v>73.29965972900391</v>
+        <v>110.7281112670898</v>
       </c>
       <c r="AK19">
-        <v>73.09893798828125</v>
+        <v>110.4248962402344</v>
       </c>
       <c r="AL19">
-        <v>73.23110198974609</v>
+        <v>110.6245498657227</v>
       </c>
       <c r="AM19">
-        <v>73.32212829589844</v>
+        <v>110.7620620727539</v>
       </c>
     </row>
     <row r="20" spans="1:39">
@@ -2770,43 +2770,43 @@
         <v>199.4013366699219</v>
       </c>
       <c r="AA20">
-        <v>73.52461242675781</v>
+        <v>111.7099227905273</v>
       </c>
       <c r="AB20">
-        <v>73.00238037109375</v>
+        <v>110.9164733886719</v>
       </c>
       <c r="AC20">
-        <v>72.88044738769531</v>
+        <v>110.7312240600586</v>
       </c>
       <c r="AD20">
-        <v>72.89891052246094</v>
+        <v>110.7592620849609</v>
       </c>
       <c r="AE20">
-        <v>72.89849853515625</v>
+        <v>110.7586364746094</v>
       </c>
       <c r="AF20">
-        <v>72.97941589355469</v>
+        <v>110.8815765380859</v>
       </c>
       <c r="AG20">
-        <v>72.86538696289062</v>
+        <v>110.7083282470703</v>
       </c>
       <c r="AH20">
-        <v>73.11961364746094</v>
+        <v>111.094596862793</v>
       </c>
       <c r="AI20">
-        <v>73.05409240722656</v>
+        <v>110.9950408935547</v>
       </c>
       <c r="AJ20">
-        <v>72.87840270996094</v>
+        <v>110.7281112670898</v>
       </c>
       <c r="AK20">
-        <v>72.6788330078125</v>
+        <v>110.4248962402344</v>
       </c>
       <c r="AL20">
-        <v>72.81024169921875</v>
+        <v>110.6245498657227</v>
       </c>
       <c r="AM20">
-        <v>72.90074920654297</v>
+        <v>110.7620620727539</v>
       </c>
     </row>
     <row r="21" spans="1:39">
@@ -6669,43 +6669,43 @@
         <v>203.2755584716797</v>
       </c>
       <c r="AA54">
-        <v>104.3912658691406</v>
+        <v>242.4226226806641</v>
       </c>
       <c r="AB54">
-        <v>104.4955596923828</v>
+        <v>242.6648406982422</v>
       </c>
       <c r="AC54">
-        <v>104.4652862548828</v>
+        <v>242.5945434570312</v>
       </c>
       <c r="AD54">
-        <v>104.352294921875</v>
+        <v>242.3321380615234</v>
       </c>
       <c r="AE54">
-        <v>104.2090606689453</v>
+        <v>241.9995269775391</v>
       </c>
       <c r="AF54">
-        <v>104.5785217285156</v>
+        <v>242.8575134277344</v>
       </c>
       <c r="AG54">
-        <v>104.6313323974609</v>
+        <v>242.9801177978516</v>
       </c>
       <c r="AH54">
-        <v>104.4594573974609</v>
+        <v>242.5809783935547</v>
       </c>
       <c r="AI54">
-        <v>104.4889068603516</v>
+        <v>242.6493835449219</v>
       </c>
       <c r="AJ54">
-        <v>104.0531463623047</v>
+        <v>241.6374359130859</v>
       </c>
       <c r="AK54">
-        <v>103.9520111083984</v>
+        <v>241.402587890625</v>
       </c>
       <c r="AL54">
-        <v>104.0540466308594</v>
+        <v>241.6395263671875</v>
       </c>
       <c r="AM54">
-        <v>104.4349670410156</v>
+        <v>242.5241394042969</v>
       </c>
     </row>
     <row r="55" spans="1:39">
@@ -6785,43 +6785,43 @@
         <v>203.2755584716797</v>
       </c>
       <c r="AA55">
-        <v>33.73452758789062</v>
+        <v>242.4226226806641</v>
       </c>
       <c r="AB55">
-        <v>33.76823425292969</v>
+        <v>242.6648406982422</v>
       </c>
       <c r="AC55">
-        <v>33.75843811035156</v>
+        <v>242.5945434570312</v>
       </c>
       <c r="AD55">
-        <v>33.721923828125</v>
+        <v>242.3321380615234</v>
       </c>
       <c r="AE55">
-        <v>33.6756591796875</v>
+        <v>241.9995269775391</v>
       </c>
       <c r="AF55">
-        <v>33.7950439453125</v>
+        <v>242.8575134277344</v>
       </c>
       <c r="AG55">
-        <v>33.81210327148438</v>
+        <v>242.9801177978516</v>
       </c>
       <c r="AH55">
-        <v>33.75656127929688</v>
+        <v>242.5809783935547</v>
       </c>
       <c r="AI55">
-        <v>33.76608276367188</v>
+        <v>242.6493835449219</v>
       </c>
       <c r="AJ55">
-        <v>33.62525939941406</v>
+        <v>241.6374359130859</v>
       </c>
       <c r="AK55">
-        <v>33.59257507324219</v>
+        <v>241.402587890625</v>
       </c>
       <c r="AL55">
-        <v>33.62554931640625</v>
+        <v>241.6395263671875</v>
       </c>
       <c r="AM55">
-        <v>33.7486572265625</v>
+        <v>242.5241394042969</v>
       </c>
     </row>
     <row r="56" spans="1:39">
@@ -8983,43 +8983,43 @@
         <v>333.7438049316406</v>
       </c>
       <c r="AA74">
-        <v>102.1043472290039</v>
+        <v>125.2101135253906</v>
       </c>
       <c r="AB74">
-        <v>100.4258422851562</v>
+        <v>123.1517715454102</v>
       </c>
       <c r="AC74">
-        <v>100.4282073974609</v>
+        <v>123.154670715332</v>
       </c>
       <c r="AD74">
-        <v>100.4141998291016</v>
+        <v>123.1374893188477</v>
       </c>
       <c r="AE74">
-        <v>100.3638916015625</v>
+        <v>123.0758056640625</v>
       </c>
       <c r="AF74">
-        <v>100.4263916015625</v>
+        <v>123.1524429321289</v>
       </c>
       <c r="AG74">
-        <v>100.4132537841797</v>
+        <v>123.1363296508789</v>
       </c>
       <c r="AH74">
-        <v>100.4145812988281</v>
+        <v>123.1379623413086</v>
       </c>
       <c r="AI74">
-        <v>100.4283294677734</v>
+        <v>123.1548156738281</v>
       </c>
       <c r="AJ74">
-        <v>100.2931747436523</v>
+        <v>122.9890823364258</v>
       </c>
       <c r="AK74">
-        <v>100.2460098266602</v>
+        <v>122.9312438964844</v>
       </c>
       <c r="AL74">
-        <v>100.3002014160156</v>
+        <v>122.9976959228516</v>
       </c>
       <c r="AM74">
-        <v>100.4352340698242</v>
+        <v>123.1632843017578</v>
       </c>
     </row>
     <row r="75" spans="1:39">
@@ -12691,43 +12691,43 @@
         <v>414.5332336425781</v>
       </c>
       <c r="AA107">
-        <v>91.12578582763672</v>
+        <v>121.2864990234375</v>
       </c>
       <c r="AB107">
-        <v>88.58495330810547</v>
+        <v>117.9047012329102</v>
       </c>
       <c r="AC107">
-        <v>88.54530334472656</v>
+        <v>117.8519287109375</v>
       </c>
       <c r="AD107">
-        <v>88.58713531494141</v>
+        <v>117.9076080322266</v>
       </c>
       <c r="AE107">
-        <v>87.75502014160156</v>
+        <v>116.8000869750977</v>
       </c>
       <c r="AF107">
-        <v>88.489990234375</v>
+        <v>117.7783126831055</v>
       </c>
       <c r="AG107">
-        <v>88.65104675292969</v>
+        <v>117.99267578125</v>
       </c>
       <c r="AH107">
-        <v>88.58136749267578</v>
+        <v>117.8999328613281</v>
       </c>
       <c r="AI107">
-        <v>88.54988861083984</v>
+        <v>117.8580322265625</v>
       </c>
       <c r="AJ107">
-        <v>87.74155426025391</v>
+        <v>116.7821578979492</v>
       </c>
       <c r="AK107">
-        <v>87.71298217773438</v>
+        <v>116.7441253662109</v>
       </c>
       <c r="AL107">
-        <v>87.64897155761719</v>
+        <v>116.658935546875</v>
       </c>
       <c r="AM107">
-        <v>88.48876953125</v>
+        <v>117.7766799926758</v>
       </c>
     </row>
     <row r="108" spans="1:39">
@@ -17358,43 +17358,43 @@
         <v>184.8026580810547</v>
       </c>
       <c r="AA147">
-        <v>89.70252227783203</v>
+        <v>136.0835876464844</v>
       </c>
       <c r="AB147">
-        <v>89.69699096679688</v>
+        <v>136.0751953125</v>
       </c>
       <c r="AC147">
-        <v>89.7532958984375</v>
+        <v>136.1606140136719</v>
       </c>
       <c r="AD147">
-        <v>89.2357177734375</v>
+        <v>135.3754119873047</v>
       </c>
       <c r="AE147">
-        <v>89.42598724365234</v>
+        <v>135.6640625</v>
       </c>
       <c r="AF147">
-        <v>89.89198303222656</v>
+        <v>136.3710174560547</v>
       </c>
       <c r="AG147">
-        <v>89.45118713378906</v>
+        <v>135.7023010253906</v>
       </c>
       <c r="AH147">
-        <v>89.54006958007812</v>
+        <v>135.8371429443359</v>
       </c>
       <c r="AI147">
-        <v>89.31695556640625</v>
+        <v>135.4986572265625</v>
       </c>
       <c r="AJ147">
-        <v>89.32870483398438</v>
+        <v>135.5164794921875</v>
       </c>
       <c r="AK147">
-        <v>89.10743713378906</v>
+        <v>135.1808013916016</v>
       </c>
       <c r="AL147">
-        <v>89.9014892578125</v>
+        <v>136.3854217529297</v>
       </c>
       <c r="AM147">
-        <v>89.80204010009766</v>
+        <v>136.2345581054688</v>
       </c>
     </row>
     <row r="148" spans="1:39">
@@ -18872,43 +18872,43 @@
         <v>199.4013366699219</v>
       </c>
       <c r="AA160">
-        <v>106.031494140625</v>
+        <v>109.2975387573242</v>
       </c>
       <c r="AB160">
-        <v>107.4295425415039</v>
+        <v>110.7386474609375</v>
       </c>
       <c r="AC160">
-        <v>107.6376113891602</v>
+        <v>110.953125</v>
       </c>
       <c r="AD160">
-        <v>107.7070541381836</v>
+        <v>111.0247116088867</v>
       </c>
       <c r="AE160">
-        <v>107.3379364013672</v>
+        <v>110.6442184448242</v>
       </c>
       <c r="AF160">
-        <v>107.4206695556641</v>
+        <v>110.7294998168945</v>
       </c>
       <c r="AG160">
-        <v>107.3233337402344</v>
+        <v>110.6291732788086</v>
       </c>
       <c r="AH160">
-        <v>107.4707412719727</v>
+        <v>110.781120300293</v>
       </c>
       <c r="AI160">
-        <v>107.7442321777344</v>
+        <v>111.0630340576172</v>
       </c>
       <c r="AJ160">
-        <v>107.0785522460938</v>
+        <v>110.3768463134766</v>
       </c>
       <c r="AK160">
-        <v>107.1667175292969</v>
+        <v>110.4677276611328</v>
       </c>
       <c r="AL160">
-        <v>107.1022644042969</v>
+        <v>110.4012908935547</v>
       </c>
       <c r="AM160">
-        <v>107.5628662109375</v>
+        <v>110.8760833740234</v>
       </c>
     </row>
     <row r="161" spans="1:39">
@@ -18988,43 +18988,43 @@
         <v>199.4013366699219</v>
       </c>
       <c r="AA161">
-        <v>73.60002899169922</v>
+        <v>109.2975387573242</v>
       </c>
       <c r="AB161">
-        <v>74.57045745849609</v>
+        <v>110.7386474609375</v>
       </c>
       <c r="AC161">
-        <v>74.71488952636719</v>
+        <v>110.953125</v>
       </c>
       <c r="AD161">
-        <v>74.76309204101562</v>
+        <v>111.0247116088867</v>
       </c>
       <c r="AE161">
-        <v>74.50686645507812</v>
+        <v>110.6442184448242</v>
       </c>
       <c r="AF161">
-        <v>74.56430053710938</v>
+        <v>110.7294998168945</v>
       </c>
       <c r="AG161">
-        <v>74.49673461914062</v>
+        <v>110.6291732788086</v>
       </c>
       <c r="AH161">
-        <v>74.59906005859375</v>
+        <v>110.781120300293</v>
       </c>
       <c r="AI161">
-        <v>74.78889465332031</v>
+        <v>111.0630340576172</v>
       </c>
       <c r="AJ161">
-        <v>74.32682800292969</v>
+        <v>110.3768463134766</v>
       </c>
       <c r="AK161">
-        <v>74.38802337646484</v>
+        <v>110.4677276611328</v>
       </c>
       <c r="AL161">
-        <v>74.34328460693359</v>
+        <v>110.4012908935547</v>
       </c>
       <c r="AM161">
-        <v>74.66300964355469</v>
+        <v>110.8760833740234</v>
       </c>
     </row>
     <row r="162" spans="1:39">
@@ -20145,43 +20145,43 @@
         <v>119.6553649902344</v>
       </c>
       <c r="AA171">
-        <v>122.9662170410156</v>
+        <v>171.8688201904297</v>
       </c>
       <c r="AB171">
-        <v>122.8535919189453</v>
+        <v>171.7113952636719</v>
       </c>
       <c r="AC171">
-        <v>122.582649230957</v>
+        <v>171.3327026367188</v>
       </c>
       <c r="AD171">
-        <v>123.2251739501953</v>
+        <v>172.2307586669922</v>
       </c>
       <c r="AE171">
-        <v>122.3205947875977</v>
+        <v>170.9664306640625</v>
       </c>
       <c r="AF171">
-        <v>122.9066009521484</v>
+        <v>171.7854919433594</v>
       </c>
       <c r="AG171">
-        <v>123.0785980224609</v>
+        <v>172.0258941650391</v>
       </c>
       <c r="AH171">
-        <v>122.9016723632812</v>
+        <v>171.7785949707031</v>
       </c>
       <c r="AI171">
-        <v>122.9480209350586</v>
+        <v>171.8433837890625</v>
       </c>
       <c r="AJ171">
-        <v>122.4913482666016</v>
+        <v>171.2050933837891</v>
       </c>
       <c r="AK171">
-        <v>122.4509735107422</v>
+        <v>171.1486663818359</v>
       </c>
       <c r="AL171">
-        <v>122.6449127197266</v>
+        <v>171.4197235107422</v>
       </c>
       <c r="AM171">
-        <v>122.4591217041016</v>
+        <v>171.1600494384766</v>
       </c>
     </row>
     <row r="172" spans="1:39">
@@ -22822,43 +22822,43 @@
         <v>203.2755584716797</v>
       </c>
       <c r="AA194">
-        <v>84.39703369140625</v>
+        <v>234.462646484375</v>
       </c>
       <c r="AB194">
-        <v>84.32366943359375</v>
+        <v>234.2588500976562</v>
       </c>
       <c r="AC194">
-        <v>84.36473083496094</v>
+        <v>234.3728790283203</v>
       </c>
       <c r="AD194">
-        <v>84.16819763183594</v>
+        <v>233.8268890380859</v>
       </c>
       <c r="AE194">
-        <v>84.12953186035156</v>
+        <v>233.7194671630859</v>
       </c>
       <c r="AF194">
-        <v>84.34231567382812</v>
+        <v>234.3106384277344</v>
       </c>
       <c r="AG194">
-        <v>84.38967895507812</v>
+        <v>234.4421997070312</v>
       </c>
       <c r="AH194">
-        <v>84.29313659667969</v>
+        <v>234.1740112304688</v>
       </c>
       <c r="AI194">
-        <v>84.37355041503906</v>
+        <v>234.3974151611328</v>
       </c>
       <c r="AJ194">
-        <v>83.93862915039062</v>
+        <v>233.1891479492188</v>
       </c>
       <c r="AK194">
-        <v>83.93782043457031</v>
+        <v>233.1869049072266</v>
       </c>
       <c r="AL194">
-        <v>84.01728820800781</v>
+        <v>233.4076690673828</v>
       </c>
       <c r="AM194">
-        <v>84.35523986816406</v>
+        <v>234.3465270996094</v>
       </c>
     </row>
     <row r="195" spans="1:39">
@@ -24339,43 +24339,43 @@
         <v>174.2201538085938</v>
       </c>
       <c r="AA207">
-        <v>52.42376708984375</v>
+        <v>245.8654022216797</v>
       </c>
       <c r="AB207">
-        <v>52.65922546386719</v>
+        <v>246.9697418212891</v>
       </c>
       <c r="AC207">
-        <v>52.67176818847656</v>
+        <v>247.0285491943359</v>
       </c>
       <c r="AD207">
-        <v>52.59109497070312</v>
+        <v>246.6501617431641</v>
       </c>
       <c r="AE207">
-        <v>52.42497253417969</v>
+        <v>245.87109375</v>
       </c>
       <c r="AF207">
-        <v>52.70724487304688</v>
+        <v>247.1949615478516</v>
       </c>
       <c r="AG207">
-        <v>52.72169494628906</v>
+        <v>247.2627258300781</v>
       </c>
       <c r="AH207">
-        <v>52.64103698730469</v>
+        <v>246.8844146728516</v>
       </c>
       <c r="AI207">
-        <v>52.67149353027344</v>
+        <v>247.0272521972656</v>
       </c>
       <c r="AJ207">
-        <v>52.39785766601562</v>
+        <v>245.743896484375</v>
       </c>
       <c r="AK207">
-        <v>52.35238647460938</v>
+        <v>245.5306091308594</v>
       </c>
       <c r="AL207">
-        <v>52.42645263671875</v>
+        <v>245.8779907226562</v>
       </c>
       <c r="AM207">
-        <v>52.65663146972656</v>
+        <v>246.9575347900391</v>
       </c>
     </row>
     <row r="208" spans="1:39">
@@ -26201,43 +26201,43 @@
         <v>333.7438049316406</v>
       </c>
       <c r="AA223">
-        <v>102.9734268188477</v>
+        <v>125.1354598999023</v>
       </c>
       <c r="AB223">
-        <v>101.011848449707</v>
+        <v>122.751708984375</v>
       </c>
       <c r="AC223">
-        <v>100.9928741455078</v>
+        <v>122.728645324707</v>
       </c>
       <c r="AD223">
-        <v>100.9786834716797</v>
+        <v>122.7114028930664</v>
       </c>
       <c r="AE223">
-        <v>100.927131652832</v>
+        <v>122.6487579345703</v>
       </c>
       <c r="AF223">
-        <v>100.9738311767578</v>
+        <v>122.7055053710938</v>
       </c>
       <c r="AG223">
-        <v>100.9810028076172</v>
+        <v>122.714225769043</v>
       </c>
       <c r="AH223">
-        <v>100.9958190917969</v>
+        <v>122.7322235107422</v>
       </c>
       <c r="AI223">
-        <v>101.0182876586914</v>
+        <v>122.7595367431641</v>
       </c>
       <c r="AJ223">
-        <v>100.8251647949219</v>
+        <v>122.5248489379883</v>
       </c>
       <c r="AK223">
-        <v>100.7885437011719</v>
+        <v>122.4803466796875</v>
       </c>
       <c r="AL223">
-        <v>100.838264465332</v>
+        <v>122.5407638549805</v>
       </c>
       <c r="AM223">
-        <v>101.0107727050781</v>
+        <v>122.7503967285156</v>
       </c>
     </row>
     <row r="224" spans="1:39">
@@ -28164,43 +28164,43 @@
         <v>384.956298828125</v>
       </c>
       <c r="AA240">
-        <v>95.71376037597656</v>
+        <v>123.7898178100586</v>
       </c>
       <c r="AB240">
-        <v>92.64635467529297</v>
+        <v>119.8226318359375</v>
       </c>
       <c r="AC240">
-        <v>92.39242553710938</v>
+        <v>119.4942169189453</v>
       </c>
       <c r="AD240">
-        <v>92.03689575195312</v>
+        <v>119.0343933105469</v>
       </c>
       <c r="AE240">
-        <v>92.78648376464844</v>
+        <v>120.0038681030273</v>
       </c>
       <c r="AF240">
-        <v>92.45703125</v>
+        <v>119.5777740478516</v>
       </c>
       <c r="AG240">
-        <v>92.62432861328125</v>
+        <v>119.7941513061523</v>
       </c>
       <c r="AH240">
-        <v>92.54192352294922</v>
+        <v>119.6875686645508</v>
       </c>
       <c r="AI240">
-        <v>92.41862487792969</v>
+        <v>119.5281066894531</v>
       </c>
       <c r="AJ240">
-        <v>91.53823852539062</v>
+        <v>118.3894729614258</v>
       </c>
       <c r="AK240">
-        <v>91.31480407714844</v>
+        <v>118.1004867553711</v>
       </c>
       <c r="AL240">
-        <v>91.46237182617188</v>
+        <v>118.2913436889648</v>
       </c>
       <c r="AM240">
-        <v>92.80892944335938</v>
+        <v>120.0328979492188</v>
       </c>
     </row>
     <row r="241" spans="1:39">
@@ -34371,43 +34371,43 @@
         <v>160.8665618896484</v>
       </c>
       <c r="AA294">
-        <v>104.0471343994141</v>
+        <v>156.7808990478516</v>
       </c>
       <c r="AB294">
-        <v>102.9936752319336</v>
+        <v>155.1935119628906</v>
       </c>
       <c r="AC294">
-        <v>103.2409133911133</v>
+        <v>155.5660552978516</v>
       </c>
       <c r="AD294">
-        <v>102.3850250244141</v>
+        <v>154.2763824462891</v>
       </c>
       <c r="AE294">
-        <v>102.2061004638672</v>
+        <v>154.0067749023438</v>
       </c>
       <c r="AF294">
-        <v>102.9808044433594</v>
+        <v>155.1741180419922</v>
       </c>
       <c r="AG294">
-        <v>102.5543518066406</v>
+        <v>154.5315246582031</v>
       </c>
       <c r="AH294">
-        <v>102.4753570556641</v>
+        <v>154.4124908447266</v>
       </c>
       <c r="AI294">
-        <v>103.3105621337891</v>
+        <v>155.6710052490234</v>
       </c>
       <c r="AJ294">
-        <v>101.8624496459961</v>
+        <v>153.4889526367188</v>
       </c>
       <c r="AK294">
-        <v>101.6306915283203</v>
+        <v>153.1397399902344</v>
       </c>
       <c r="AL294">
-        <v>101.5736999511719</v>
+        <v>153.0538635253906</v>
       </c>
       <c r="AM294">
-        <v>102.3717803955078</v>
+        <v>154.2564239501953</v>
       </c>
     </row>
     <row r="295" spans="1:39">
@@ -36117,43 +36117,43 @@
         <v>319.6206970214844</v>
       </c>
       <c r="AA309">
-        <v>123.228271484375</v>
+        <v>144.4783782958984</v>
       </c>
       <c r="AB309">
-        <v>122.6178588867188</v>
+        <v>143.7626953125</v>
       </c>
       <c r="AC309">
-        <v>121.3096008300781</v>
+        <v>142.2288360595703</v>
       </c>
       <c r="AD309">
-        <v>122.0988082885742</v>
+        <v>143.1541442871094</v>
       </c>
       <c r="AE309">
-        <v>118.8957214355469</v>
+        <v>139.3986968994141</v>
       </c>
       <c r="AF309">
-        <v>122.8647155761719</v>
+        <v>144.0521240234375</v>
       </c>
       <c r="AG309">
-        <v>122.5874252319336</v>
+        <v>143.7270202636719</v>
       </c>
       <c r="AH309">
-        <v>122.1579208374023</v>
+        <v>143.2234497070312</v>
       </c>
       <c r="AI309">
-        <v>122.3959426879883</v>
+        <v>143.5025177001953</v>
       </c>
       <c r="AJ309">
-        <v>118.1355285644531</v>
+        <v>138.5074157714844</v>
       </c>
       <c r="AK309">
-        <v>118.8339385986328</v>
+        <v>139.3262634277344</v>
       </c>
       <c r="AL309">
-        <v>118.6128234863281</v>
+        <v>139.0670166015625</v>
       </c>
       <c r="AM309">
-        <v>123.1211929321289</v>
+        <v>144.3528289794922</v>
       </c>
     </row>
     <row r="310" spans="1:39">
@@ -42765,43 +42765,43 @@
         <v>333.3076782226562</v>
       </c>
       <c r="AA366">
-        <v>82.17811584472656</v>
+        <v>122.1534652709961</v>
       </c>
       <c r="AB366">
-        <v>80.85764312744141</v>
+        <v>120.1906585693359</v>
       </c>
       <c r="AC366">
-        <v>80.48965454101562</v>
+        <v>119.6436538696289</v>
       </c>
       <c r="AD366">
-        <v>80.55705261230469</v>
+        <v>119.7438430786133</v>
       </c>
       <c r="AE366">
-        <v>76.80386352539062</v>
+        <v>114.164924621582</v>
       </c>
       <c r="AF366">
-        <v>80.67210388183594</v>
+        <v>119.9148559570312</v>
       </c>
       <c r="AG366">
-        <v>80.89669036865234</v>
+        <v>120.2486953735352</v>
       </c>
       <c r="AH366">
-        <v>80.49789428710938</v>
+        <v>119.6558990478516</v>
       </c>
       <c r="AI366">
-        <v>80.63904571533203</v>
+        <v>119.86572265625</v>
       </c>
       <c r="AJ366">
-        <v>76.95304870605469</v>
+        <v>114.3866729736328</v>
       </c>
       <c r="AK366">
-        <v>75.993408203125</v>
+        <v>112.9602279663086</v>
       </c>
       <c r="AL366">
-        <v>76.72537231445312</v>
+        <v>114.0482482910156</v>
       </c>
       <c r="AM366">
-        <v>80.3621826171875</v>
+        <v>119.4541778564453</v>
       </c>
     </row>
     <row r="367" spans="1:39">
@@ -43702,43 +43702,43 @@
         <v>60.65530395507812</v>
       </c>
       <c r="AA374">
-        <v>63.67588424682617</v>
+        <v>90.3726806640625</v>
       </c>
       <c r="AB374">
-        <v>45.91639709472656</v>
+        <v>65.16733551025391</v>
       </c>
       <c r="AC374">
-        <v>14.53071403503418</v>
+        <v>20.62287139892578</v>
       </c>
       <c r="AD374">
-        <v>41.73450469970703</v>
+        <v>59.23214340209961</v>
       </c>
       <c r="AE374">
-        <v>36.40813064575195</v>
+        <v>51.67263031005859</v>
       </c>
       <c r="AF374">
-        <v>42.60133361816406</v>
+        <v>60.46239852905273</v>
       </c>
       <c r="AG374">
-        <v>39.75069808959961</v>
+        <v>56.41660308837891</v>
       </c>
       <c r="AH374">
-        <v>44.92907333374023</v>
+        <v>63.76606750488281</v>
       </c>
       <c r="AI374">
-        <v>47.23564147949219</v>
+        <v>67.03968811035156</v>
       </c>
       <c r="AJ374">
-        <v>41.81766510009766</v>
+        <v>59.35017013549805</v>
       </c>
       <c r="AK374">
-        <v>38.29426193237305</v>
+        <v>54.34954071044922</v>
       </c>
       <c r="AL374">
-        <v>38.7247314453125</v>
+        <v>54.96048736572266</v>
       </c>
       <c r="AM374">
-        <v>39.45144271850586</v>
+        <v>55.99188232421875</v>
       </c>
     </row>
     <row r="375" spans="1:39">
@@ -47344,43 +47344,43 @@
         <v>199.4013366699219</v>
       </c>
       <c r="AA407">
-        <v>65.92037963867188</v>
+        <v>97.34323120117188</v>
       </c>
       <c r="AB407">
-        <v>66.15798950195312</v>
+        <v>97.69410705566406</v>
       </c>
       <c r="AC407">
-        <v>66.27480316162109</v>
+        <v>97.86660766601562</v>
       </c>
       <c r="AD407">
-        <v>66.06764221191406</v>
+        <v>97.56069183349609</v>
       </c>
       <c r="AE407">
-        <v>66.40789031982422</v>
+        <v>98.06313323974609</v>
       </c>
       <c r="AF407">
-        <v>66.48386383056641</v>
+        <v>98.17532348632812</v>
       </c>
       <c r="AG407">
-        <v>66.80355834960938</v>
+        <v>98.64740753173828</v>
       </c>
       <c r="AH407">
-        <v>65.96556091308594</v>
+        <v>97.40995025634766</v>
       </c>
       <c r="AI407">
-        <v>66.37056732177734</v>
+        <v>98.00801849365234</v>
       </c>
       <c r="AJ407">
-        <v>65.46554565429688</v>
+        <v>96.67159271240234</v>
       </c>
       <c r="AK407">
-        <v>66.18183898925781</v>
+        <v>97.72932434082031</v>
       </c>
       <c r="AL407">
-        <v>65.61503601074219</v>
+        <v>96.89234161376953</v>
       </c>
       <c r="AM407">
-        <v>66.98346710205078</v>
+        <v>98.91307830810547</v>
       </c>
     </row>
     <row r="408" spans="1:39">
@@ -48635,43 +48635,43 @@
         <v>160.8665618896484</v>
       </c>
       <c r="AA418">
-        <v>93.68794250488281</v>
+        <v>154.2834320068359</v>
       </c>
       <c r="AB418">
-        <v>92.58885955810547</v>
+        <v>152.4734802246094</v>
       </c>
       <c r="AC418">
-        <v>91.90348815917969</v>
+        <v>151.3448181152344</v>
       </c>
       <c r="AD418">
-        <v>92.37542724609375</v>
+        <v>152.1220092773438</v>
       </c>
       <c r="AE418">
-        <v>91.26089477539062</v>
+        <v>150.28662109375</v>
       </c>
       <c r="AF418">
-        <v>92.50468444824219</v>
+        <v>152.3348541259766</v>
       </c>
       <c r="AG418">
-        <v>92.39698028564453</v>
+        <v>152.1575012207031</v>
       </c>
       <c r="AH418">
-        <v>93.25248718261719</v>
+        <v>153.5663299560547</v>
       </c>
       <c r="AI418">
-        <v>92.77798461914062</v>
+        <v>152.7849273681641</v>
       </c>
       <c r="AJ418">
-        <v>91.22415161132812</v>
+        <v>150.2261047363281</v>
       </c>
       <c r="AK418">
-        <v>90.87973022460938</v>
+        <v>149.6589202880859</v>
       </c>
       <c r="AL418">
-        <v>91.54013061523438</v>
+        <v>150.7464447021484</v>
       </c>
       <c r="AM418">
-        <v>92.92729187011719</v>
+        <v>153.0308074951172</v>
       </c>
     </row>
     <row r="419" spans="1:39">
@@ -54937,43 +54937,43 @@
         <v>333.7438049316406</v>
       </c>
       <c r="AA473">
-        <v>160.8297119140625</v>
+        <v>167.4623107910156</v>
       </c>
       <c r="AB473">
-        <v>153.4622497558594</v>
+        <v>159.791015625</v>
       </c>
       <c r="AC473">
-        <v>133.7812652587891</v>
+        <v>139.2983856201172</v>
       </c>
       <c r="AD473">
-        <v>156.8799285888672</v>
+        <v>163.3496398925781</v>
       </c>
       <c r="AE473">
-        <v>152.3667755126953</v>
+        <v>158.6503601074219</v>
       </c>
       <c r="AF473">
-        <v>145.592529296875</v>
+        <v>151.5967559814453</v>
       </c>
       <c r="AG473">
-        <v>155.4173889160156</v>
+        <v>161.8267822265625</v>
       </c>
       <c r="AH473">
-        <v>167.8958282470703</v>
+        <v>174.8198394775391</v>
       </c>
       <c r="AI473">
-        <v>153.9184417724609</v>
+        <v>160.2660217285156</v>
       </c>
       <c r="AJ473">
-        <v>143.5005798339844</v>
+        <v>149.4185333251953</v>
       </c>
       <c r="AK473">
-        <v>147.6265563964844</v>
+        <v>153.7146606445312</v>
       </c>
       <c r="AL473">
-        <v>149.9217834472656</v>
+        <v>156.1045379638672</v>
       </c>
       <c r="AM473">
-        <v>163.6392211914062</v>
+        <v>170.3876800537109</v>
       </c>
     </row>
     <row r="474" spans="1:39">
